--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_R2.xlsx
@@ -451,49 +451,49 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.002723038929463795</v>
+        <v>0.002723037705999909</v>
       </c>
       <c r="D2">
-        <v>0.01973441721868208</v>
+        <v>0.01973441336465609</v>
       </c>
       <c r="E2">
-        <v>0.04378066166732242</v>
+        <v>0.04378066367148359</v>
       </c>
       <c r="F2">
-        <v>0.0609686220273995</v>
+        <v>0.06096862009203041</v>
       </c>
       <c r="G2">
-        <v>0.09599601572450545</v>
+        <v>0.09599601361102605</v>
       </c>
       <c r="H2">
-        <v>0.1737783723408517</v>
+        <v>0.1737783714441264</v>
       </c>
       <c r="I2">
-        <v>0.2234855590082824</v>
+        <v>0.2234855682771539</v>
       </c>
       <c r="J2">
-        <v>0.3173262258441519</v>
+        <v>0.3173262388498396</v>
       </c>
       <c r="K2">
-        <v>0.373597940815963</v>
+        <v>0.3735979526137118</v>
       </c>
       <c r="L2">
-        <v>0.4131317653708206</v>
+        <v>0.4131317742262844</v>
       </c>
       <c r="M2">
-        <v>0.5318822522833975</v>
+        <v>0.5318822776357406</v>
       </c>
       <c r="N2">
-        <v>0.5917948210725604</v>
+        <v>0.5917948353917323</v>
       </c>
       <c r="O2">
-        <v>0.6895138164027352</v>
+        <v>0.6895138300648926</v>
       </c>
       <c r="P2">
-        <v>0.7624334950628282</v>
+        <v>0.7624335114271983</v>
       </c>
       <c r="Q2">
-        <v>0.787640075145319</v>
+        <v>0.7876400887985079</v>
       </c>
     </row>
     <row r="3">
@@ -506,49 +506,49 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.03351742271212166</v>
+        <v>0.0335174173111098</v>
       </c>
       <c r="D3">
-        <v>0.1651601529804766</v>
+        <v>0.1651602816636193</v>
       </c>
       <c r="E3">
-        <v>0.3007881657654893</v>
+        <v>0.300788144713201</v>
       </c>
       <c r="F3">
-        <v>0.3508660045516099</v>
+        <v>0.3508659612327936</v>
       </c>
       <c r="G3">
-        <v>0.4295092641482666</v>
+        <v>0.4295092635139964</v>
       </c>
       <c r="H3">
-        <v>0.495580985626306</v>
+        <v>0.4955810015499931</v>
       </c>
       <c r="I3">
-        <v>0.589659847417956</v>
+        <v>0.589659868561816</v>
       </c>
       <c r="J3">
-        <v>0.6444911911449197</v>
+        <v>0.6444912184406093</v>
       </c>
       <c r="K3">
-        <v>0.6915937050876377</v>
+        <v>0.6915937397717411</v>
       </c>
       <c r="L3">
-        <v>0.7310154767967854</v>
+        <v>0.7310155175754296</v>
       </c>
       <c r="M3">
-        <v>0.7555573606421351</v>
+        <v>0.7555574113938172</v>
       </c>
       <c r="N3">
-        <v>0.7920122153232126</v>
+        <v>0.7920122880237237</v>
       </c>
       <c r="O3">
-        <v>0.8269708736323306</v>
+        <v>0.8269709612143035</v>
       </c>
       <c r="P3">
-        <v>0.8668947562022489</v>
+        <v>0.8668948596101546</v>
       </c>
       <c r="Q3">
-        <v>0.884410946562983</v>
+        <v>0.8844110449473035</v>
       </c>
     </row>
     <row r="4">
@@ -561,49 +561,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.002095491878692846</v>
+        <v>0.002095490885072326</v>
       </c>
       <c r="D4">
-        <v>0.005773563953130001</v>
+        <v>0.005773560412335565</v>
       </c>
       <c r="E4">
-        <v>0.02995847307089206</v>
+        <v>0.02995844134360381</v>
       </c>
       <c r="F4">
-        <v>0.04529767877313995</v>
+        <v>0.04529767922211558</v>
       </c>
       <c r="G4">
-        <v>0.1513246342190707</v>
+        <v>0.1513246234267625</v>
       </c>
       <c r="H4">
-        <v>0.233793664603677</v>
+        <v>0.2337936729028711</v>
       </c>
       <c r="I4">
-        <v>0.2989266230427348</v>
+        <v>0.2989266278503357</v>
       </c>
       <c r="J4">
-        <v>0.4117475153382459</v>
+        <v>0.4117475119752916</v>
       </c>
       <c r="K4">
-        <v>0.4600814241117218</v>
+        <v>0.460081445959203</v>
       </c>
       <c r="L4">
-        <v>0.5638023432139945</v>
+        <v>0.5638023690719156</v>
       </c>
       <c r="M4">
-        <v>0.6463744226939652</v>
+        <v>0.6463744496106443</v>
       </c>
       <c r="N4">
-        <v>0.7058547079011697</v>
+        <v>0.7058547295791421</v>
       </c>
       <c r="O4">
-        <v>0.7414169505238952</v>
+        <v>0.7414169720138766</v>
       </c>
       <c r="P4">
-        <v>0.7585413447559487</v>
+        <v>0.7585413668777375</v>
       </c>
       <c r="Q4">
-        <v>0.7786824043173378</v>
+        <v>0.7786824340525074</v>
       </c>
     </row>
     <row r="5">
@@ -616,49 +616,49 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.009423747151691142</v>
+        <v>0.009423744704149417</v>
       </c>
       <c r="D5">
-        <v>0.06192592747206072</v>
+        <v>0.06192593218097919</v>
       </c>
       <c r="E5">
-        <v>0.1526000152306405</v>
+        <v>0.1526004050747829</v>
       </c>
       <c r="F5">
-        <v>0.3005112577498245</v>
+        <v>0.3005112493758525</v>
       </c>
       <c r="G5">
-        <v>0.3712997523571636</v>
+        <v>0.3712997403249606</v>
       </c>
       <c r="H5">
-        <v>0.523305726151291</v>
+        <v>0.5233057586282885</v>
       </c>
       <c r="I5">
-        <v>0.566627971649645</v>
+        <v>0.5666280010362137</v>
       </c>
       <c r="J5">
-        <v>0.63790707109619</v>
+        <v>0.6379071449165632</v>
       </c>
       <c r="K5">
-        <v>0.6743178092460315</v>
+        <v>0.6743178506240708</v>
       </c>
       <c r="L5">
-        <v>0.7045300990826817</v>
+        <v>0.7045301424102877</v>
       </c>
       <c r="M5">
-        <v>0.7465621926041082</v>
+        <v>0.7465622465991754</v>
       </c>
       <c r="N5">
-        <v>0.7673024823816379</v>
+        <v>0.7673025412970634</v>
       </c>
       <c r="O5">
-        <v>0.7924209566584712</v>
+        <v>0.7924210161410108</v>
       </c>
       <c r="P5">
-        <v>0.8077856248319032</v>
+        <v>0.8077856907703582</v>
       </c>
       <c r="Q5">
-        <v>0.8308395635648822</v>
+        <v>0.8308396371050203</v>
       </c>
     </row>
     <row r="6">
@@ -671,49 +671,49 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.006391824904337207</v>
+        <v>0.006391822500690036</v>
       </c>
       <c r="D6">
-        <v>0.05720736647241975</v>
+        <v>0.05720739409611064</v>
       </c>
       <c r="E6">
-        <v>0.1119050232324904</v>
+        <v>0.111905253718327</v>
       </c>
       <c r="F6">
-        <v>0.3370605025616139</v>
+        <v>0.3370604582989438</v>
       </c>
       <c r="G6">
-        <v>0.4063124270033293</v>
+        <v>0.4063123890326872</v>
       </c>
       <c r="H6">
-        <v>0.5386239156826436</v>
+        <v>0.5386239313494063</v>
       </c>
       <c r="I6">
-        <v>0.5938288985303596</v>
+        <v>0.5938288816853505</v>
       </c>
       <c r="J6">
-        <v>0.6252085997883606</v>
+        <v>0.6252086180155161</v>
       </c>
       <c r="K6">
-        <v>0.66883305150854</v>
+        <v>0.6688330725184333</v>
       </c>
       <c r="L6">
-        <v>0.6941781486820761</v>
+        <v>0.6941781717773197</v>
       </c>
       <c r="M6">
-        <v>0.7355253286128063</v>
+        <v>0.7355253623665302</v>
       </c>
       <c r="N6">
-        <v>0.7613817206142861</v>
+        <v>0.7613817567232722</v>
       </c>
       <c r="O6">
-        <v>0.7841144919581982</v>
+        <v>0.7841145258745299</v>
       </c>
       <c r="P6">
-        <v>0.8017134998319826</v>
+        <v>0.8017135474339934</v>
       </c>
       <c r="Q6">
-        <v>0.8271192773773712</v>
+        <v>0.8271193274364377</v>
       </c>
     </row>
     <row r="7">
@@ -726,49 +726,49 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.002192969171317172</v>
+        <v>0.002192968096434544</v>
       </c>
       <c r="D7">
-        <v>0.006588965462423158</v>
+        <v>0.006588962011855104</v>
       </c>
       <c r="E7">
-        <v>0.02035677996657081</v>
+        <v>0.02035676982053092</v>
       </c>
       <c r="F7">
-        <v>0.03795988853451182</v>
+        <v>0.03795988348509682</v>
       </c>
       <c r="G7">
-        <v>0.09667505266163368</v>
+        <v>0.09667507040110423</v>
       </c>
       <c r="H7">
-        <v>0.1922853986878716</v>
+        <v>0.1922853920538672</v>
       </c>
       <c r="I7">
-        <v>0.27398641082883</v>
+        <v>0.2739864227052873</v>
       </c>
       <c r="J7">
-        <v>0.3327209678472626</v>
+        <v>0.3327209751821594</v>
       </c>
       <c r="K7">
-        <v>0.4294938265718891</v>
+        <v>0.429493812160491</v>
       </c>
       <c r="L7">
-        <v>0.4865550180130207</v>
+        <v>0.4865550431995682</v>
       </c>
       <c r="M7">
-        <v>0.6140266298929511</v>
+        <v>0.6140266538099626</v>
       </c>
       <c r="N7">
-        <v>0.709519715682617</v>
+        <v>0.7095197332419488</v>
       </c>
       <c r="O7">
-        <v>0.7272520146765793</v>
+        <v>0.7272520273238163</v>
       </c>
       <c r="P7">
-        <v>0.7628594883990687</v>
+        <v>0.7628595109049982</v>
       </c>
       <c r="Q7">
-        <v>0.7882271155653913</v>
+        <v>0.7882271390048995</v>
       </c>
     </row>
     <row r="8">
@@ -781,49 +781,49 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.003084993111213907</v>
+        <v>0.003084991517069424</v>
       </c>
       <c r="D8">
-        <v>0.006360608502831488</v>
+        <v>0.006360605496873561</v>
       </c>
       <c r="E8">
-        <v>0.03266112381237796</v>
+        <v>0.0326611290757215</v>
       </c>
       <c r="F8">
-        <v>0.1470178435082368</v>
+        <v>0.1470178519541909</v>
       </c>
       <c r="G8">
-        <v>0.2009409360953304</v>
+        <v>0.200940936808799</v>
       </c>
       <c r="H8">
-        <v>0.2780851945667607</v>
+        <v>0.278085221002354</v>
       </c>
       <c r="I8">
-        <v>0.3313311850833552</v>
+        <v>0.3313312005922353</v>
       </c>
       <c r="J8">
-        <v>0.4542921482793522</v>
+        <v>0.4542921844070296</v>
       </c>
       <c r="K8">
-        <v>0.5049913663870516</v>
+        <v>0.5049913949038508</v>
       </c>
       <c r="L8">
-        <v>0.6422090364131851</v>
+        <v>0.6422090588613882</v>
       </c>
       <c r="M8">
-        <v>0.6819604146281784</v>
+        <v>0.6819604337146732</v>
       </c>
       <c r="N8">
-        <v>0.7243891810334773</v>
+        <v>0.7243891947971943</v>
       </c>
       <c r="O8">
-        <v>0.7438862149845313</v>
+        <v>0.7438862299912062</v>
       </c>
       <c r="P8">
-        <v>0.7603772400335059</v>
+        <v>0.7603772586036766</v>
       </c>
       <c r="Q8">
-        <v>0.7780313044146674</v>
+        <v>0.7780313275639685</v>
       </c>
     </row>
     <row r="9">
@@ -836,49 +836,49 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.003066166589238528</v>
+        <v>0.003066164997128973</v>
       </c>
       <c r="D9">
-        <v>0.006171733526849299</v>
+        <v>0.006171730360430505</v>
       </c>
       <c r="E9">
-        <v>0.02961106150415627</v>
+        <v>0.02961106559825832</v>
       </c>
       <c r="F9">
-        <v>0.1282665703860597</v>
+        <v>0.1282665787151722</v>
       </c>
       <c r="G9">
-        <v>0.1745370557434526</v>
+        <v>0.1745370563383738</v>
       </c>
       <c r="H9">
-        <v>0.2395523241635189</v>
+        <v>0.2395523482443138</v>
       </c>
       <c r="I9">
-        <v>0.2806916154506324</v>
+        <v>0.2806916334235978</v>
       </c>
       <c r="J9">
-        <v>0.3833290563600693</v>
+        <v>0.3833290906440978</v>
       </c>
       <c r="K9">
-        <v>0.4176439893691493</v>
+        <v>0.4176440153711131</v>
       </c>
       <c r="L9">
-        <v>0.5760472650059767</v>
+        <v>0.5760472792981979</v>
       </c>
       <c r="M9">
-        <v>0.608240927453656</v>
+        <v>0.6082409483907201</v>
       </c>
       <c r="N9">
-        <v>0.6249777762732511</v>
+        <v>0.6249777956680989</v>
       </c>
       <c r="O9">
-        <v>0.6560929044487611</v>
+        <v>0.656092926691931</v>
       </c>
       <c r="P9">
-        <v>0.6661907029640366</v>
+        <v>0.6661907306866931</v>
       </c>
       <c r="Q9">
-        <v>0.6851375389649264</v>
+        <v>0.6851375636335142</v>
       </c>
     </row>
     <row r="10">
@@ -891,49 +891,49 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.003066052436127675</v>
+        <v>0.003066050844770185</v>
       </c>
       <c r="D10">
-        <v>0.006171782479068244</v>
+        <v>0.00617177931629076</v>
       </c>
       <c r="E10">
-        <v>0.02969097725713488</v>
+        <v>0.02969098142080773</v>
       </c>
       <c r="F10">
-        <v>0.1279116286493697</v>
+        <v>0.1279116373470925</v>
       </c>
       <c r="G10">
-        <v>0.1738890554771397</v>
+        <v>0.1738890559767001</v>
       </c>
       <c r="H10">
-        <v>0.2392688590283856</v>
+        <v>0.2392688829520643</v>
       </c>
       <c r="I10">
-        <v>0.27944689325489</v>
+        <v>0.2794469113894789</v>
       </c>
       <c r="J10">
-        <v>0.3799918596719717</v>
+        <v>0.3799918929899098</v>
       </c>
       <c r="K10">
-        <v>0.4133951133504459</v>
+        <v>0.4133951382449479</v>
       </c>
       <c r="L10">
-        <v>0.5674978373626203</v>
+        <v>0.5674978504057511</v>
       </c>
       <c r="M10">
-        <v>0.6002784243010225</v>
+        <v>0.6002784467060105</v>
       </c>
       <c r="N10">
-        <v>0.6141870796803706</v>
+        <v>0.6141871059638792</v>
       </c>
       <c r="O10">
-        <v>0.6425314762477425</v>
+        <v>0.6425315000798384</v>
       </c>
       <c r="P10">
-        <v>0.6542849896912214</v>
+        <v>0.6542850287536914</v>
       </c>
       <c r="Q10">
-        <v>0.672568123637165</v>
+        <v>0.672568151031788</v>
       </c>
     </row>
     <row r="11">
@@ -946,49 +946,49 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.003070895938557805</v>
+        <v>0.003070894346063557</v>
       </c>
       <c r="D11">
-        <v>0.006213113683565918</v>
+        <v>0.006213110554025181</v>
       </c>
       <c r="E11">
-        <v>0.03004412528198708</v>
+        <v>0.03004412945162915</v>
       </c>
       <c r="F11">
-        <v>0.126000783100542</v>
+        <v>0.1260007912674501</v>
       </c>
       <c r="G11">
-        <v>0.1704197676557629</v>
+        <v>0.170419769073172</v>
       </c>
       <c r="H11">
-        <v>0.2355913012721843</v>
+        <v>0.2355913253259827</v>
       </c>
       <c r="I11">
-        <v>0.2771197810621415</v>
+        <v>0.2771197993157548</v>
       </c>
       <c r="J11">
-        <v>0.3824472836581625</v>
+        <v>0.3824473185566071</v>
       </c>
       <c r="K11">
-        <v>0.4202423136326923</v>
+        <v>0.4202423395947577</v>
       </c>
       <c r="L11">
-        <v>0.5721033339573749</v>
+        <v>0.5721033461219909</v>
       </c>
       <c r="M11">
-        <v>0.6052276285880621</v>
+        <v>0.6052276444931576</v>
       </c>
       <c r="N11">
-        <v>0.6276795952289507</v>
+        <v>0.62767961130035</v>
       </c>
       <c r="O11">
-        <v>0.6511627230397441</v>
+        <v>0.6511627428337829</v>
       </c>
       <c r="P11">
-        <v>0.6694578449043322</v>
+        <v>0.6694578773279417</v>
       </c>
       <c r="Q11">
-        <v>0.6803492510249509</v>
+        <v>0.680349310526867</v>
       </c>
     </row>
     <row r="12">
@@ -1001,49 +1001,49 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.00984539776587734</v>
+        <v>0.009845395137291102</v>
       </c>
       <c r="D12">
-        <v>0.06218273943922425</v>
+        <v>0.06218274304875471</v>
       </c>
       <c r="E12">
-        <v>0.1524420919292423</v>
+        <v>0.1524425114761624</v>
       </c>
       <c r="F12">
-        <v>0.2582927610929162</v>
+        <v>0.2582927373346793</v>
       </c>
       <c r="G12">
-        <v>0.3933484538278635</v>
+        <v>0.3933484477083946</v>
       </c>
       <c r="H12">
-        <v>0.5365660355674028</v>
+        <v>0.5365660362560323</v>
       </c>
       <c r="I12">
-        <v>0.5739375602721899</v>
+        <v>0.5739375714543379</v>
       </c>
       <c r="J12">
-        <v>0.6469435270516595</v>
+        <v>0.6469435764208844</v>
       </c>
       <c r="K12">
-        <v>0.6843535153341738</v>
+        <v>0.6843535530488372</v>
       </c>
       <c r="L12">
-        <v>0.7119793826809638</v>
+        <v>0.7119794230495069</v>
       </c>
       <c r="M12">
-        <v>0.7558651062096577</v>
+        <v>0.7558651625225729</v>
       </c>
       <c r="N12">
-        <v>0.7756597881136081</v>
+        <v>0.775659849089261</v>
       </c>
       <c r="O12">
-        <v>0.7974163852546746</v>
+        <v>0.7974164512127403</v>
       </c>
       <c r="P12">
-        <v>0.8097401222710991</v>
+        <v>0.8097401906317991</v>
       </c>
       <c r="Q12">
-        <v>0.8366793768670422</v>
+        <v>0.8366794453806417</v>
       </c>
     </row>
     <row r="13">
@@ -1056,49 +1056,49 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0.01347154639938863</v>
+        <v>0.01347154513613436</v>
       </c>
       <c r="D13">
-        <v>0.1081460933098917</v>
+        <v>0.1081460987557561</v>
       </c>
       <c r="E13">
-        <v>0.1794170517436121</v>
+        <v>0.1794170874979811</v>
       </c>
       <c r="F13">
-        <v>0.2789226145040477</v>
+        <v>0.278922637925251</v>
       </c>
       <c r="G13">
-        <v>0.3281164130173919</v>
+        <v>0.3281164053866096</v>
       </c>
       <c r="H13">
-        <v>0.4506659140426591</v>
+        <v>0.4506659142093515</v>
       </c>
       <c r="I13">
-        <v>0.5412971384227425</v>
+        <v>0.5412971270303876</v>
       </c>
       <c r="J13">
-        <v>0.598229912868691</v>
+        <v>0.5982298224670232</v>
       </c>
       <c r="K13">
-        <v>0.6635100269236762</v>
+        <v>0.6635099924692875</v>
       </c>
       <c r="L13">
-        <v>0.7146494437797576</v>
+        <v>0.7146494695905505</v>
       </c>
       <c r="M13">
-        <v>0.7362616720577613</v>
+        <v>0.7362617067263819</v>
       </c>
       <c r="N13">
-        <v>0.7714399967903849</v>
+        <v>0.7714400395115908</v>
       </c>
       <c r="O13">
-        <v>0.7837641195752014</v>
+        <v>0.7837641675974549</v>
       </c>
       <c r="P13">
-        <v>0.8048373777044596</v>
+        <v>0.8048374337246146</v>
       </c>
       <c r="Q13">
-        <v>0.8227299791943359</v>
+        <v>0.8227300408569742</v>
       </c>
     </row>
     <row r="14">
@@ -1111,49 +1111,49 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0.002187363093658301</v>
+        <v>0.002187362019095529</v>
       </c>
       <c r="D14">
-        <v>0.006528706576494736</v>
+        <v>0.006528703100397437</v>
       </c>
       <c r="E14">
-        <v>0.01956895164989436</v>
+        <v>0.01956894182258984</v>
       </c>
       <c r="F14">
-        <v>0.03571908307092597</v>
+        <v>0.03571907828981846</v>
       </c>
       <c r="G14">
-        <v>0.08845251861902448</v>
+        <v>0.08845253505892847</v>
       </c>
       <c r="H14">
-        <v>0.1714661962069941</v>
+        <v>0.1714661921018904</v>
       </c>
       <c r="I14">
-        <v>0.2414388019133219</v>
+        <v>0.2414388137369442</v>
       </c>
       <c r="J14">
-        <v>0.2869332363363711</v>
+        <v>0.2869332474267751</v>
       </c>
       <c r="K14">
-        <v>0.3726804960998961</v>
+        <v>0.3726804811585245</v>
       </c>
       <c r="L14">
-        <v>0.430003939573795</v>
+        <v>0.430003962121556</v>
       </c>
       <c r="M14">
-        <v>0.5419043639948785</v>
+        <v>0.5419043798860437</v>
       </c>
       <c r="N14">
-        <v>0.6445195478868786</v>
+        <v>0.6445195608028513</v>
       </c>
       <c r="O14">
-        <v>0.6631786026235492</v>
+        <v>0.6631786178238843</v>
       </c>
       <c r="P14">
-        <v>0.6979952472832334</v>
+        <v>0.697995268041794</v>
       </c>
       <c r="Q14">
-        <v>0.7202304438856888</v>
+        <v>0.7202304670054873</v>
       </c>
     </row>
     <row r="15">
@@ -1166,49 +1166,49 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0.002184750180993511</v>
+        <v>0.002184749107436823</v>
       </c>
       <c r="D15">
-        <v>0.006505803748539152</v>
+        <v>0.006505800268302164</v>
       </c>
       <c r="E15">
-        <v>0.01927876234891091</v>
+        <v>0.0192787526948931</v>
       </c>
       <c r="F15">
-        <v>0.03487073172658073</v>
+        <v>0.03487072711893435</v>
       </c>
       <c r="G15">
-        <v>0.08519691033280363</v>
+        <v>0.08519692623081421</v>
       </c>
       <c r="H15">
-        <v>0.1644948214719173</v>
+        <v>0.1644948180004635</v>
       </c>
       <c r="I15">
-        <v>0.2323261548406768</v>
+        <v>0.2323261666932441</v>
       </c>
       <c r="J15">
-        <v>0.2761882116831529</v>
+        <v>0.2761882239066785</v>
       </c>
       <c r="K15">
-        <v>0.3575338940302832</v>
+        <v>0.3575338822515463</v>
       </c>
       <c r="L15">
-        <v>0.4152982292260283</v>
+        <v>0.4152982532718734</v>
       </c>
       <c r="M15">
-        <v>0.5197393975362135</v>
+        <v>0.5197394165034386</v>
       </c>
       <c r="N15">
-        <v>0.6184069269358627</v>
+        <v>0.6184069433453103</v>
       </c>
       <c r="O15">
-        <v>0.6352315661203424</v>
+        <v>0.6352315847262741</v>
       </c>
       <c r="P15">
-        <v>0.6666032500183717</v>
+        <v>0.6666032751492502</v>
       </c>
       <c r="Q15">
-        <v>0.6893895636240452</v>
+        <v>0.6893895910819294</v>
       </c>
     </row>
     <row r="16">
@@ -1221,49 +1221,49 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0.002182012395091859</v>
+        <v>0.002182011322163446</v>
       </c>
       <c r="D16">
-        <v>0.006482916180119869</v>
+        <v>0.006482912690531806</v>
       </c>
       <c r="E16">
-        <v>0.01902651316653914</v>
+        <v>0.0190265035744287</v>
       </c>
       <c r="F16">
-        <v>0.03427142652479132</v>
+        <v>0.03427142188191945</v>
       </c>
       <c r="G16">
-        <v>0.08389368193972024</v>
+        <v>0.08389369779418232</v>
       </c>
       <c r="H16">
-        <v>0.1634907151662888</v>
+        <v>0.1634907115570911</v>
       </c>
       <c r="I16">
-        <v>0.2313240727797509</v>
+        <v>0.2313240848878297</v>
       </c>
       <c r="J16">
-        <v>0.2737931770978294</v>
+        <v>0.2737931900854698</v>
       </c>
       <c r="K16">
-        <v>0.3526707717787724</v>
+        <v>0.3526707607595779</v>
       </c>
       <c r="L16">
-        <v>0.4099353685489233</v>
+        <v>0.4099353938293654</v>
       </c>
       <c r="M16">
-        <v>0.5144321513927519</v>
+        <v>0.5144321720541367</v>
       </c>
       <c r="N16">
-        <v>0.6135408599583427</v>
+        <v>0.6135408769254849</v>
       </c>
       <c r="O16">
-        <v>0.6333625530874596</v>
+        <v>0.6333625723585814</v>
       </c>
       <c r="P16">
-        <v>0.6676480186268193</v>
+        <v>0.6676480439128076</v>
       </c>
       <c r="Q16">
-        <v>0.6906440275191161</v>
+        <v>0.6906440550850439</v>
       </c>
     </row>
     <row r="17">
@@ -1276,49 +1276,49 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0.002181023368567736</v>
+        <v>0.002181022296654844</v>
       </c>
       <c r="D17">
-        <v>0.006482689457453339</v>
+        <v>0.006482685968419166</v>
       </c>
       <c r="E17">
-        <v>0.01901532607016476</v>
+        <v>0.01901531653917798</v>
       </c>
       <c r="F17">
-        <v>0.03416148814200137</v>
+        <v>0.03416148343724867</v>
       </c>
       <c r="G17">
-        <v>0.08267166417946703</v>
+        <v>0.08267167971264233</v>
       </c>
       <c r="H17">
-        <v>0.1608599713024386</v>
+        <v>0.1608599682259624</v>
       </c>
       <c r="I17">
-        <v>0.228856638317426</v>
+        <v>0.2288566502673816</v>
       </c>
       <c r="J17">
-        <v>0.2674724667488156</v>
+        <v>0.2674724815456353</v>
       </c>
       <c r="K17">
-        <v>0.3408594503828025</v>
+        <v>0.3408594408923267</v>
       </c>
       <c r="L17">
-        <v>0.398358119511487</v>
+        <v>0.3983581449060892</v>
       </c>
       <c r="M17">
-        <v>0.4989695939401551</v>
+        <v>0.4989696164237194</v>
       </c>
       <c r="N17">
-        <v>0.5868480513604223</v>
+        <v>0.5868480716890134</v>
       </c>
       <c r="O17">
-        <v>0.6123294722154635</v>
+        <v>0.6123294952230292</v>
       </c>
       <c r="P17">
-        <v>0.6507623350340452</v>
+        <v>0.6507623631870859</v>
       </c>
       <c r="Q17">
-        <v>0.6729150774276182</v>
+        <v>0.67291510865796</v>
       </c>
     </row>
     <row r="18">
@@ -1331,49 +1331,49 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0.009803218541614034</v>
+        <v>0.009803215947621902</v>
       </c>
       <c r="D18">
-        <v>0.06169837002995493</v>
+        <v>0.06169837333939299</v>
       </c>
       <c r="E18">
-        <v>0.158406641871943</v>
+        <v>0.1584070980721992</v>
       </c>
       <c r="F18">
-        <v>0.2695537138208902</v>
+        <v>0.2695536934000458</v>
       </c>
       <c r="G18">
-        <v>0.3941643900701847</v>
+        <v>0.3941643542912614</v>
       </c>
       <c r="H18">
-        <v>0.5337123934833046</v>
+        <v>0.5337124206573898</v>
       </c>
       <c r="I18">
-        <v>0.6545326240451992</v>
+        <v>0.654532624642709</v>
       </c>
       <c r="J18">
-        <v>0.6822244561778165</v>
+        <v>0.6822244166418761</v>
       </c>
       <c r="K18">
-        <v>0.6975392769725721</v>
+        <v>0.6975389154171568</v>
       </c>
       <c r="L18">
-        <v>0.7078021664105194</v>
+        <v>0.7078021749272658</v>
       </c>
       <c r="M18">
-        <v>0.7559560711594484</v>
+        <v>0.7559561233993339</v>
       </c>
       <c r="N18">
-        <v>0.7765765823540018</v>
+        <v>0.7765766386716659</v>
       </c>
       <c r="O18">
-        <v>0.8022195418541312</v>
+        <v>0.8022195983506389</v>
       </c>
       <c r="P18">
-        <v>0.8245196930282007</v>
+        <v>0.8245197306451435</v>
       </c>
       <c r="Q18">
-        <v>0.8452260299917881</v>
+        <v>0.8452260749520376</v>
       </c>
     </row>
     <row r="19">
@@ -1386,49 +1386,49 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0.006696296304751992</v>
+        <v>0.006696293811250809</v>
       </c>
       <c r="D19">
-        <v>0.05674612047356198</v>
+        <v>0.05674614441906001</v>
       </c>
       <c r="E19">
-        <v>0.1134700955573801</v>
+        <v>0.1134703975192324</v>
       </c>
       <c r="F19">
-        <v>0.3131467719901885</v>
+        <v>0.3131467122590161</v>
       </c>
       <c r="G19">
-        <v>0.4130953052871617</v>
+        <v>0.413095273009453</v>
       </c>
       <c r="H19">
-        <v>0.5129727036946911</v>
+        <v>0.512972707693464</v>
       </c>
       <c r="I19">
-        <v>0.5516562592706815</v>
+        <v>0.5516562653229958</v>
       </c>
       <c r="J19">
-        <v>0.6186361021718694</v>
+        <v>0.6186361222438596</v>
       </c>
       <c r="K19">
-        <v>0.6619802504879457</v>
+        <v>0.6619802718846823</v>
       </c>
       <c r="L19">
-        <v>0.6937276043508365</v>
+        <v>0.6937276281181974</v>
       </c>
       <c r="M19">
-        <v>0.7410533053955328</v>
+        <v>0.7410533356623843</v>
       </c>
       <c r="N19">
-        <v>0.7674925718573051</v>
+        <v>0.7674926051956484</v>
       </c>
       <c r="O19">
-        <v>0.7983174602344904</v>
+        <v>0.7983174899219139</v>
       </c>
       <c r="P19">
-        <v>0.8113032239514903</v>
+        <v>0.8113032630551817</v>
       </c>
       <c r="Q19">
-        <v>0.8360492624839494</v>
+        <v>0.8360493061752546</v>
       </c>
     </row>
     <row r="20">
@@ -1441,49 +1441,49 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0.005936472761896128</v>
+        <v>0.005936470190776366</v>
       </c>
       <c r="D20">
-        <v>0.08699080666187742</v>
+        <v>0.0869909252848432</v>
       </c>
       <c r="E20">
-        <v>0.1184976617950313</v>
+        <v>0.1184977094956787</v>
       </c>
       <c r="F20">
-        <v>0.2402932129064006</v>
+        <v>0.2402932171504587</v>
       </c>
       <c r="G20">
-        <v>0.3454446627103118</v>
+        <v>0.3454446845922131</v>
       </c>
       <c r="H20">
-        <v>0.4537481357953815</v>
+        <v>0.4537482014088902</v>
       </c>
       <c r="I20">
-        <v>0.5046376937142263</v>
+        <v>0.5046377248075353</v>
       </c>
       <c r="J20">
-        <v>0.5806443232295002</v>
+        <v>0.5806443503058651</v>
       </c>
       <c r="K20">
-        <v>0.6064158624719307</v>
+        <v>0.6064158868982293</v>
       </c>
       <c r="L20">
-        <v>0.6740173480015963</v>
+        <v>0.6740173849043702</v>
       </c>
       <c r="M20">
-        <v>0.7092175376278333</v>
+        <v>0.7092175722019435</v>
       </c>
       <c r="N20">
-        <v>0.7475518778178123</v>
+        <v>0.7475519189396308</v>
       </c>
       <c r="O20">
-        <v>0.7673403951597915</v>
+        <v>0.76734043889752</v>
       </c>
       <c r="P20">
-        <v>0.7902657825112627</v>
+        <v>0.7902658294568182</v>
       </c>
       <c r="Q20">
-        <v>0.8075618309443635</v>
+        <v>0.8075618730484149</v>
       </c>
     </row>
     <row r="21">
@@ -1496,49 +1496,49 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0.03318963886345039</v>
+        <v>0.03318963351676674</v>
       </c>
       <c r="D21">
-        <v>0.1513718719406744</v>
+        <v>0.1513719895680388</v>
       </c>
       <c r="E21">
-        <v>0.2694098775539364</v>
+        <v>0.2694098635972275</v>
       </c>
       <c r="F21">
-        <v>0.319878676790714</v>
+        <v>0.3198786289391131</v>
       </c>
       <c r="G21">
-        <v>0.3845088737130732</v>
+        <v>0.3845088495181905</v>
       </c>
       <c r="H21">
-        <v>0.4565913027928286</v>
+        <v>0.4565913209907824</v>
       </c>
       <c r="I21">
-        <v>0.5655970071852852</v>
+        <v>0.5655970346647917</v>
       </c>
       <c r="J21">
-        <v>0.6381410839842152</v>
+        <v>0.6381411128693359</v>
       </c>
       <c r="K21">
-        <v>0.6896095349504343</v>
+        <v>0.6896095736582261</v>
       </c>
       <c r="L21">
-        <v>0.7358659487836368</v>
+        <v>0.7358660063597133</v>
       </c>
       <c r="M21">
-        <v>0.7678969898517907</v>
+        <v>0.7678970614218807</v>
       </c>
       <c r="N21">
-        <v>0.7952508376541699</v>
+        <v>0.7952509189164383</v>
       </c>
       <c r="O21">
-        <v>0.8261536139736423</v>
+        <v>0.8261537115397233</v>
       </c>
       <c r="P21">
-        <v>0.8651579420279286</v>
+        <v>0.865158046078838</v>
       </c>
       <c r="Q21">
-        <v>0.8844620804460707</v>
+        <v>0.8844621929044891</v>
       </c>
     </row>
     <row r="22">
@@ -1551,49 +1551,49 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0.03318976526592121</v>
+        <v>0.03318975991685791</v>
       </c>
       <c r="D22">
-        <v>0.1533655433418709</v>
+        <v>0.1533656658764254</v>
       </c>
       <c r="E22">
-        <v>0.267396985445098</v>
+        <v>0.2673969740185888</v>
       </c>
       <c r="F22">
-        <v>0.3167968360535743</v>
+        <v>0.316796792579185</v>
       </c>
       <c r="G22">
-        <v>0.3769821010306686</v>
+        <v>0.3769820751990482</v>
       </c>
       <c r="H22">
-        <v>0.4410262248379587</v>
+        <v>0.4410262452532646</v>
       </c>
       <c r="I22">
-        <v>0.5457652759804967</v>
+        <v>0.5457653086536021</v>
       </c>
       <c r="J22">
-        <v>0.6136371112573701</v>
+        <v>0.6136371411206754</v>
       </c>
       <c r="K22">
-        <v>0.6715141754230693</v>
+        <v>0.6715142084759675</v>
       </c>
       <c r="L22">
-        <v>0.7214820723999806</v>
+        <v>0.7214821215837588</v>
       </c>
       <c r="M22">
-        <v>0.7694804396751314</v>
+        <v>0.7694805171698469</v>
       </c>
       <c r="N22">
-        <v>0.8021745249785588</v>
+        <v>0.8021746169629379</v>
       </c>
       <c r="O22">
-        <v>0.8363609499219065</v>
+        <v>0.8363610568786994</v>
       </c>
       <c r="P22">
-        <v>0.8566212985723048</v>
+        <v>0.8566214086016095</v>
       </c>
       <c r="Q22">
-        <v>0.874057178153467</v>
+        <v>0.8740572846903158</v>
       </c>
     </row>
     <row r="23">
@@ -1606,49 +1606,49 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0.01160257680067101</v>
+        <v>0.0116025747907933</v>
       </c>
       <c r="D23">
-        <v>0.1148183384090449</v>
+        <v>0.1148182622520663</v>
       </c>
       <c r="E23">
-        <v>0.2418588938403936</v>
+        <v>0.241858872117835</v>
       </c>
       <c r="F23">
-        <v>0.2930160887592863</v>
+        <v>0.2930160685960898</v>
       </c>
       <c r="G23">
-        <v>0.507321498136958</v>
+        <v>0.5073214861738087</v>
       </c>
       <c r="H23">
-        <v>0.5910784628878338</v>
+        <v>0.5910784867726013</v>
       </c>
       <c r="I23">
-        <v>0.641461796528791</v>
+        <v>0.6414618326852768</v>
       </c>
       <c r="J23">
-        <v>0.7022572477432896</v>
+        <v>0.7022573076871244</v>
       </c>
       <c r="K23">
-        <v>0.7411838828863399</v>
+        <v>0.7411839613873865</v>
       </c>
       <c r="L23">
-        <v>0.8005558681303501</v>
+        <v>0.800555947570729</v>
       </c>
       <c r="M23">
-        <v>0.8300468216043996</v>
+        <v>0.830046906883784</v>
       </c>
       <c r="N23">
-        <v>0.876189607447775</v>
+        <v>0.8761896511094236</v>
       </c>
       <c r="O23">
-        <v>0.8920389964162021</v>
+        <v>0.8920390385005835</v>
       </c>
       <c r="P23">
-        <v>0.9053216905461393</v>
+        <v>0.9053217126953312</v>
       </c>
       <c r="Q23">
-        <v>0.9212634585050095</v>
+        <v>0.9212634513639341</v>
       </c>
     </row>
     <row r="24">
@@ -1661,49 +1661,49 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0.002408526164219937</v>
+        <v>0.002408533821229963</v>
       </c>
       <c r="D24">
-        <v>0.008757276027620664</v>
+        <v>0.008757272379105174</v>
       </c>
       <c r="E24">
-        <v>0.04474539628632446</v>
+        <v>0.04474540321641152</v>
       </c>
       <c r="F24">
-        <v>0.07725856554591481</v>
+        <v>0.07725847591564217</v>
       </c>
       <c r="G24">
-        <v>0.1109523647806381</v>
+        <v>0.110952357553174</v>
       </c>
       <c r="H24">
-        <v>0.1543517085940515</v>
+        <v>0.1543517185690323</v>
       </c>
       <c r="I24">
-        <v>0.1934288866478031</v>
+        <v>0.1934288895134784</v>
       </c>
       <c r="J24">
-        <v>0.38672951241237</v>
+        <v>0.3867295476758459</v>
       </c>
       <c r="K24">
-        <v>0.561244428877292</v>
+        <v>0.5612444781397609</v>
       </c>
       <c r="L24">
-        <v>0.6563324641296227</v>
+        <v>0.6563325272785374</v>
       </c>
       <c r="M24">
-        <v>0.7050647337331537</v>
+        <v>0.7050648192067073</v>
       </c>
       <c r="N24">
-        <v>0.7760206709891155</v>
+        <v>0.7760207567604984</v>
       </c>
       <c r="O24">
-        <v>0.8248632797419442</v>
+        <v>0.824863365265606</v>
       </c>
       <c r="P24">
-        <v>0.8455384416494164</v>
+        <v>0.8455385274479279</v>
       </c>
       <c r="Q24">
-        <v>0.8720634734660417</v>
+        <v>0.8720635499864402</v>
       </c>
     </row>
     <row r="25">
@@ -1716,49 +1716,49 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0.002714603445934216</v>
+        <v>0.002714611831829083</v>
       </c>
       <c r="D25">
-        <v>0.01077488566975382</v>
+        <v>0.01077487961947809</v>
       </c>
       <c r="E25">
-        <v>0.05665401111206148</v>
+        <v>0.0566540209373142</v>
       </c>
       <c r="F25">
-        <v>0.09324114524634719</v>
+        <v>0.09324107071225374</v>
       </c>
       <c r="G25">
-        <v>0.1034913238207988</v>
+        <v>0.1034913018998035</v>
       </c>
       <c r="H25">
-        <v>0.1513160196174929</v>
+        <v>0.1513160317765658</v>
       </c>
       <c r="I25">
-        <v>0.3459851871550539</v>
+        <v>0.3459851416035928</v>
       </c>
       <c r="J25">
-        <v>0.392885882372899</v>
+        <v>0.3928859161883136</v>
       </c>
       <c r="K25">
-        <v>0.463799676663599</v>
+        <v>0.4637997127712495</v>
       </c>
       <c r="L25">
-        <v>0.6480403438324381</v>
+        <v>0.6480404032673694</v>
       </c>
       <c r="M25">
-        <v>0.680708765126278</v>
+        <v>0.6807088367739385</v>
       </c>
       <c r="N25">
-        <v>0.7338765257019791</v>
+        <v>0.7338766178532004</v>
       </c>
       <c r="O25">
-        <v>0.7867964588803753</v>
+        <v>0.7867965477614931</v>
       </c>
       <c r="P25">
-        <v>0.828700619133345</v>
+        <v>0.8287007064636027</v>
       </c>
       <c r="Q25">
-        <v>0.8495537779724185</v>
+        <v>0.8495538657990949</v>
       </c>
     </row>
     <row r="26">
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0.009379657425210075</v>
+        <v>0.009379712579936084</v>
       </c>
       <c r="D26">
-        <v>0.01934536421008548</v>
+        <v>0.01934535007423566</v>
       </c>
       <c r="E26">
-        <v>0.05409405756167451</v>
+        <v>0.0540940636117988</v>
       </c>
       <c r="F26">
-        <v>0.1052627157411434</v>
+        <v>0.1052626947754142</v>
       </c>
       <c r="G26">
-        <v>0.1293365536491762</v>
+        <v>0.1293365519985387</v>
       </c>
       <c r="H26">
-        <v>0.1673296717088679</v>
+        <v>0.1673296780476659</v>
       </c>
       <c r="I26">
-        <v>0.3890809299582073</v>
+        <v>0.389080949473722</v>
       </c>
       <c r="J26">
-        <v>0.5606032711693634</v>
+        <v>0.5606037237706634</v>
       </c>
       <c r="K26">
-        <v>0.5954239970409327</v>
+        <v>0.5954240525791493</v>
       </c>
       <c r="L26">
-        <v>0.6842993426809856</v>
+        <v>0.6842994096142019</v>
       </c>
       <c r="M26">
-        <v>0.7356773952780691</v>
+        <v>0.7356774859109407</v>
       </c>
       <c r="N26">
-        <v>0.8044276801201046</v>
+        <v>0.8044277745584268</v>
       </c>
       <c r="O26">
-        <v>0.8366182265606905</v>
+        <v>0.8366183168546323</v>
       </c>
       <c r="P26">
-        <v>0.8544506633820678</v>
+        <v>0.8544507491905232</v>
       </c>
       <c r="Q26">
-        <v>0.8806313992206467</v>
+        <v>0.8806314753768844</v>
       </c>
     </row>
     <row r="27">
@@ -1826,49 +1826,49 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.008663746054376253</v>
+        <v>0.008663797211525548</v>
       </c>
       <c r="D27">
-        <v>0.01790862727689124</v>
+        <v>0.01790861481083317</v>
       </c>
       <c r="E27">
-        <v>0.04912101592766061</v>
+        <v>0.04912102205703006</v>
       </c>
       <c r="F27">
-        <v>0.08995385948217294</v>
+        <v>0.08995384348901003</v>
       </c>
       <c r="G27">
-        <v>0.1084414796356122</v>
+        <v>0.1084414783775891</v>
       </c>
       <c r="H27">
-        <v>0.1318609985903132</v>
+        <v>0.1318610037932377</v>
       </c>
       <c r="I27">
-        <v>0.2604308968032151</v>
+        <v>0.2604309069846061</v>
       </c>
       <c r="J27">
-        <v>0.3898231669347078</v>
+        <v>0.3898236627963031</v>
       </c>
       <c r="K27">
-        <v>0.4288997636972938</v>
+        <v>0.4288997956650792</v>
       </c>
       <c r="L27">
-        <v>0.5422676701469101</v>
+        <v>0.542267696507047</v>
       </c>
       <c r="M27">
-        <v>0.5830295836208021</v>
+        <v>0.5830296149016567</v>
       </c>
       <c r="N27">
-        <v>0.6641625139608073</v>
+        <v>0.6641625882478122</v>
       </c>
       <c r="O27">
-        <v>0.6835953149612963</v>
+        <v>0.6835954254688863</v>
       </c>
       <c r="P27">
-        <v>0.7006253775788599</v>
+        <v>0.7006254663526048</v>
       </c>
       <c r="Q27">
-        <v>0.719614687427504</v>
+        <v>0.7196147761290133</v>
       </c>
     </row>
     <row r="28">
@@ -1881,49 +1881,49 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0.002543824757351265</v>
+        <v>0.002543832589675277</v>
       </c>
       <c r="D28">
-        <v>0.009986620336946972</v>
+        <v>0.009986615225320628</v>
       </c>
       <c r="E28">
-        <v>0.05133917070049832</v>
+        <v>0.0513391802160853</v>
       </c>
       <c r="F28">
-        <v>0.08069752145753695</v>
+        <v>0.08069746068494543</v>
       </c>
       <c r="G28">
-        <v>0.08850139590244033</v>
+        <v>0.08850138301835242</v>
       </c>
       <c r="H28">
-        <v>0.12076767152055</v>
+        <v>0.1207676794574002</v>
       </c>
       <c r="I28">
-        <v>0.2343030907602058</v>
+        <v>0.2343030496239897</v>
       </c>
       <c r="J28">
-        <v>0.2642238096513813</v>
+        <v>0.2642238259913122</v>
       </c>
       <c r="K28">
-        <v>0.3159435952919579</v>
+        <v>0.3159436134727905</v>
       </c>
       <c r="L28">
-        <v>0.4959708961233432</v>
+        <v>0.4959709240269232</v>
       </c>
       <c r="M28">
-        <v>0.5400096763014907</v>
+        <v>0.5400097096760306</v>
       </c>
       <c r="N28">
-        <v>0.5662339999232373</v>
+        <v>0.5662340357512465</v>
       </c>
       <c r="O28">
-        <v>0.6184832194275693</v>
+        <v>0.6184832575498826</v>
       </c>
       <c r="P28">
-        <v>0.6592048267960622</v>
+        <v>0.6592048935809754</v>
       </c>
       <c r="Q28">
-        <v>0.6893994512225359</v>
+        <v>0.6893995395994146</v>
       </c>
     </row>
     <row r="29">
@@ -1936,49 +1936,49 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0.002542672537104607</v>
+        <v>0.002542680356070082</v>
       </c>
       <c r="D29">
-        <v>0.0100285831785174</v>
+        <v>0.01002857802347101</v>
       </c>
       <c r="E29">
-        <v>0.05125561435964099</v>
+        <v>0.05125562401053585</v>
       </c>
       <c r="F29">
-        <v>0.08084902466812871</v>
+        <v>0.08084896385328211</v>
       </c>
       <c r="G29">
-        <v>0.08863527390089132</v>
+        <v>0.0886352612355894</v>
       </c>
       <c r="H29">
-        <v>0.1209152033161167</v>
+        <v>0.1209152113506089</v>
       </c>
       <c r="I29">
-        <v>0.2275655664215197</v>
+        <v>0.2275655227623684</v>
       </c>
       <c r="J29">
-        <v>0.2604012424915525</v>
+        <v>0.2604012598900827</v>
       </c>
       <c r="K29">
-        <v>0.313084010767699</v>
+        <v>0.3130840290066426</v>
       </c>
       <c r="L29">
-        <v>0.4801808112663151</v>
+        <v>0.4801808371123037</v>
       </c>
       <c r="M29">
-        <v>0.5329007002870114</v>
+        <v>0.5329007330618827</v>
       </c>
       <c r="N29">
-        <v>0.5603226156835255</v>
+        <v>0.5603226493223361</v>
       </c>
       <c r="O29">
-        <v>0.6148728783572306</v>
+        <v>0.614872910142216</v>
       </c>
       <c r="P29">
-        <v>0.6561619551121233</v>
+        <v>0.6561620139927506</v>
       </c>
       <c r="Q29">
-        <v>0.686650497234383</v>
+        <v>0.6866505791672537</v>
       </c>
     </row>
     <row r="30">
@@ -1991,49 +1991,49 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.002513194363387594</v>
+        <v>0.002513202087044308</v>
       </c>
       <c r="D30">
-        <v>0.009909058892739409</v>
+        <v>0.009909053878713103</v>
       </c>
       <c r="E30">
-        <v>0.0505793582627081</v>
+        <v>0.05057936781417116</v>
       </c>
       <c r="F30">
-        <v>0.07918294043672969</v>
+        <v>0.07918287868481633</v>
       </c>
       <c r="G30">
-        <v>0.08721932995420145</v>
+        <v>0.08721932052233494</v>
       </c>
       <c r="H30">
-        <v>0.1185305849164326</v>
+        <v>0.1185305929319405</v>
       </c>
       <c r="I30">
-        <v>0.2188931157213969</v>
+        <v>0.2188930713734917</v>
       </c>
       <c r="J30">
-        <v>0.2531103289527175</v>
+        <v>0.2531103469897688</v>
       </c>
       <c r="K30">
-        <v>0.30694141368154</v>
+        <v>0.3069414321143066</v>
       </c>
       <c r="L30">
-        <v>0.4686284805856908</v>
+        <v>0.4686285054537943</v>
       </c>
       <c r="M30">
-        <v>0.524750111372249</v>
+        <v>0.5247501431081565</v>
       </c>
       <c r="N30">
-        <v>0.5508688625782159</v>
+        <v>0.550868893890176</v>
       </c>
       <c r="O30">
-        <v>0.6081686862191171</v>
+        <v>0.6081687123782652</v>
       </c>
       <c r="P30">
-        <v>0.6510343857455889</v>
+        <v>0.6510344403457216</v>
       </c>
       <c r="Q30">
-        <v>0.6818357482776819</v>
+        <v>0.6818358280584249</v>
       </c>
     </row>
     <row r="31">
@@ -2046,49 +2046,49 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0.00246088027732172</v>
+        <v>0.00246088782768572</v>
       </c>
       <c r="D31">
-        <v>0.009715751583561971</v>
+        <v>0.009715746804967118</v>
       </c>
       <c r="E31">
-        <v>0.04955177481350126</v>
+        <v>0.04955178426842433</v>
       </c>
       <c r="F31">
-        <v>0.07649585570618433</v>
+        <v>0.07649579306494869</v>
       </c>
       <c r="G31">
-        <v>0.08518564616134017</v>
+        <v>0.08518564090467007</v>
       </c>
       <c r="H31">
-        <v>0.1149236838504777</v>
+        <v>0.1149236922816579</v>
       </c>
       <c r="I31">
-        <v>0.2007159596179301</v>
+        <v>0.2007159174900942</v>
       </c>
       <c r="J31">
-        <v>0.2379442727777521</v>
+        <v>0.2379442939694095</v>
       </c>
       <c r="K31">
-        <v>0.2933050824326719</v>
+        <v>0.293305103937019</v>
       </c>
       <c r="L31">
-        <v>0.4391503470002155</v>
+        <v>0.4391503724922269</v>
       </c>
       <c r="M31">
-        <v>0.5071654425315706</v>
+        <v>0.5071654750340003</v>
       </c>
       <c r="N31">
-        <v>0.5317370698024696</v>
+        <v>0.5317370991636998</v>
       </c>
       <c r="O31">
-        <v>0.5944436450781114</v>
+        <v>0.5944436552409558</v>
       </c>
       <c r="P31">
-        <v>0.6406983656925953</v>
+        <v>0.640698398082476</v>
       </c>
       <c r="Q31">
-        <v>0.6746668319758056</v>
+        <v>0.6746668916027896</v>
       </c>
     </row>
     <row r="32">
@@ -2101,49 +2101,49 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.002596651443072195</v>
+        <v>0.002596659447664074</v>
       </c>
       <c r="D32">
-        <v>0.01021745671489294</v>
+        <v>0.01021745132840057</v>
       </c>
       <c r="E32">
-        <v>0.05279771436849345</v>
+        <v>0.05279772404197636</v>
       </c>
       <c r="F32">
-        <v>0.08393275898225638</v>
+        <v>0.08393269755308641</v>
       </c>
       <c r="G32">
-        <v>0.09191684246749388</v>
+        <v>0.09191682511514876</v>
       </c>
       <c r="H32">
-        <v>0.1268213238953271</v>
+        <v>0.1268213325945404</v>
       </c>
       <c r="I32">
-        <v>0.2540971370653532</v>
+        <v>0.2540970991422637</v>
       </c>
       <c r="J32">
-        <v>0.2832745985411897</v>
+        <v>0.283274615542996</v>
       </c>
       <c r="K32">
-        <v>0.3357134035238348</v>
+        <v>0.3357134232292385</v>
       </c>
       <c r="L32">
-        <v>0.5204341512075825</v>
+        <v>0.5204341846829744</v>
       </c>
       <c r="M32">
-        <v>0.56382316467956</v>
+        <v>0.5638232056686736</v>
       </c>
       <c r="N32">
-        <v>0.5942931242303622</v>
+        <v>0.5942931735915531</v>
       </c>
       <c r="O32">
-        <v>0.6471144136019886</v>
+        <v>0.6471144723941711</v>
       </c>
       <c r="P32">
-        <v>0.6873004719185893</v>
+        <v>0.6873005527626279</v>
       </c>
       <c r="Q32">
-        <v>0.7269026026183254</v>
+        <v>0.7269027027658461</v>
       </c>
     </row>
     <row r="33">
@@ -2156,49 +2156,49 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.002581435255734288</v>
+        <v>0.002581443211433498</v>
       </c>
       <c r="D33">
-        <v>0.01014897219805566</v>
+        <v>0.01014896689498102</v>
       </c>
       <c r="E33">
-        <v>0.05228885259468519</v>
+        <v>0.05228886223207074</v>
       </c>
       <c r="F33">
-        <v>0.08276715793586309</v>
+        <v>0.08276709717198472</v>
       </c>
       <c r="G33">
-        <v>0.09062501545994506</v>
+        <v>0.09062499962047033</v>
       </c>
       <c r="H33">
-        <v>0.1244057581518296</v>
+        <v>0.124405766607224</v>
       </c>
       <c r="I33">
-        <v>0.2453284078213054</v>
+        <v>0.245328370656122</v>
       </c>
       <c r="J33">
-        <v>0.2740878360436964</v>
+        <v>0.2740878531330208</v>
       </c>
       <c r="K33">
-        <v>0.3253546650780696</v>
+        <v>0.3253546847011449</v>
       </c>
       <c r="L33">
-        <v>0.5097946963226545</v>
+        <v>0.5097947276033739</v>
       </c>
       <c r="M33">
-        <v>0.5551004816377425</v>
+        <v>0.5551005193225645</v>
       </c>
       <c r="N33">
-        <v>0.5850851867943012</v>
+        <v>0.5850852300435081</v>
       </c>
       <c r="O33">
-        <v>0.6356356901597382</v>
+        <v>0.6356357382410373</v>
       </c>
       <c r="P33">
-        <v>0.6757704600621939</v>
+        <v>0.6757705302573439</v>
       </c>
       <c r="Q33">
-        <v>0.7150310580861375</v>
+        <v>0.7150311518730175</v>
       </c>
     </row>
     <row r="34">
@@ -2211,49 +2211,49 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.002571683213422271</v>
+        <v>0.002571691137235765</v>
       </c>
       <c r="D34">
-        <v>0.01010924658501899</v>
+        <v>0.01010924133951807</v>
       </c>
       <c r="E34">
-        <v>0.05190555249240469</v>
+        <v>0.05190556214508957</v>
       </c>
       <c r="F34">
-        <v>0.08199353697944978</v>
+        <v>0.08199347672732327</v>
       </c>
       <c r="G34">
-        <v>0.08976997517958796</v>
+        <v>0.08976996042730978</v>
       </c>
       <c r="H34">
-        <v>0.1227607192859576</v>
+        <v>0.1227607276284166</v>
       </c>
       <c r="I34">
-        <v>0.2371479496805348</v>
+        <v>0.2371479128966547</v>
       </c>
       <c r="J34">
-        <v>0.2655348122967823</v>
+        <v>0.2655348289948457</v>
       </c>
       <c r="K34">
-        <v>0.3156508205518321</v>
+        <v>0.315650839222127</v>
       </c>
       <c r="L34">
-        <v>0.5002150735894725</v>
+        <v>0.5002151006105036</v>
       </c>
       <c r="M34">
-        <v>0.5478737365551403</v>
+        <v>0.547873769866369</v>
       </c>
       <c r="N34">
-        <v>0.5765629983355631</v>
+        <v>0.5765630356406531</v>
       </c>
       <c r="O34">
-        <v>0.625711234430041</v>
+        <v>0.6257112752267903</v>
       </c>
       <c r="P34">
-        <v>0.6644859035624469</v>
+        <v>0.6644859675464883</v>
       </c>
       <c r="Q34">
-        <v>0.7000454976853671</v>
+        <v>0.7000455883676184</v>
       </c>
     </row>
     <row r="35">
@@ -2266,49 +2266,49 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0.002562321090404995</v>
+        <v>0.002562328982669726</v>
       </c>
       <c r="D35">
-        <v>0.01007696120751589</v>
+        <v>0.01007695600497172</v>
       </c>
       <c r="E35">
-        <v>0.05156584390237096</v>
+        <v>0.05156585355527354</v>
       </c>
       <c r="F35">
-        <v>0.08132148375998405</v>
+        <v>0.08132142322318681</v>
       </c>
       <c r="G35">
-        <v>0.08915809868820179</v>
+        <v>0.08915808555862703</v>
       </c>
       <c r="H35">
-        <v>0.1217236151494298</v>
+        <v>0.1217236234441414</v>
       </c>
       <c r="I35">
-        <v>0.2315858708038864</v>
+        <v>0.2315858334130971</v>
       </c>
       <c r="J35">
-        <v>0.2605845654807024</v>
+        <v>0.2605845823731557</v>
       </c>
       <c r="K35">
-        <v>0.3103784221256807</v>
+        <v>0.3103784404732449</v>
       </c>
       <c r="L35">
-        <v>0.4917857326361686</v>
+        <v>0.4917857578584757</v>
       </c>
       <c r="M35">
-        <v>0.5414781668361766</v>
+        <v>0.5414781984656658</v>
       </c>
       <c r="N35">
-        <v>0.5685622205244407</v>
+        <v>0.568562255113665</v>
       </c>
       <c r="O35">
-        <v>0.6161710064366732</v>
+        <v>0.6161710433353231</v>
       </c>
       <c r="P35">
-        <v>0.6548850341503225</v>
+        <v>0.654885095231493</v>
       </c>
       <c r="Q35">
-        <v>0.6870691402468828</v>
+        <v>0.6870692285199731</v>
       </c>
     </row>
     <row r="36">
@@ -2321,49 +2321,49 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.00250938663390321</v>
+        <v>0.002509394324718084</v>
       </c>
       <c r="D36">
-        <v>0.009953036614735122</v>
+        <v>0.009953031555252956</v>
       </c>
       <c r="E36">
-        <v>0.05030368797365536</v>
+        <v>0.05030369768595955</v>
       </c>
       <c r="F36">
-        <v>0.07915443524913457</v>
+        <v>0.07915437256491442</v>
       </c>
       <c r="G36">
-        <v>0.08739882409183652</v>
+        <v>0.08739881602694055</v>
       </c>
       <c r="H36">
-        <v>0.1186092115049416</v>
+        <v>0.1186092199217437</v>
       </c>
       <c r="I36">
-        <v>0.2028910476658317</v>
+        <v>0.2028910074943865</v>
       </c>
       <c r="J36">
-        <v>0.2412517349665778</v>
+        <v>0.2412517562882941</v>
       </c>
       <c r="K36">
-        <v>0.2940853769534846</v>
+        <v>0.2940853991155297</v>
       </c>
       <c r="L36">
-        <v>0.4294743198190446</v>
+        <v>0.4294743494936276</v>
       </c>
       <c r="M36">
-        <v>0.5052248501482446</v>
+        <v>0.5052248876523393</v>
       </c>
       <c r="N36">
-        <v>0.533453545276295</v>
+        <v>0.5334535796141783</v>
       </c>
       <c r="O36">
-        <v>0.5893732048292761</v>
+        <v>0.5893732252053601</v>
       </c>
       <c r="P36">
-        <v>0.6349884087415614</v>
+        <v>0.6349884418524718</v>
       </c>
       <c r="Q36">
-        <v>0.6738571492192909</v>
+        <v>0.6738572098381709</v>
       </c>
     </row>
     <row r="37">
@@ -2376,49 +2376,49 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0.03631357773237576</v>
+        <v>0.03631342024734929</v>
       </c>
       <c r="D37">
-        <v>0.1520189530634138</v>
+        <v>0.1520189172220099</v>
       </c>
       <c r="E37">
-        <v>0.1786254179459398</v>
+        <v>0.1786254150907848</v>
       </c>
       <c r="F37">
-        <v>0.2944881820031472</v>
+        <v>0.2944881923412375</v>
       </c>
       <c r="G37">
-        <v>0.4383324151670811</v>
+        <v>0.438332506478405</v>
       </c>
       <c r="H37">
-        <v>0.5204849831588543</v>
+        <v>0.5204851243968983</v>
       </c>
       <c r="I37">
-        <v>0.6272670040467765</v>
+        <v>0.6272671635849225</v>
       </c>
       <c r="J37">
-        <v>0.6587316524580055</v>
+        <v>0.6587317888426945</v>
       </c>
       <c r="K37">
-        <v>0.6928474594429024</v>
+        <v>0.6928475888825285</v>
       </c>
       <c r="L37">
-        <v>0.7529398435855833</v>
+        <v>0.752939992950401</v>
       </c>
       <c r="M37">
-        <v>0.7908321827973699</v>
+        <v>0.7908323530367137</v>
       </c>
       <c r="N37">
-        <v>0.8185242123496982</v>
+        <v>0.8185244051662945</v>
       </c>
       <c r="O37">
-        <v>0.8486802892120544</v>
+        <v>0.8486805130122086</v>
       </c>
       <c r="P37">
-        <v>0.8668502740998534</v>
+        <v>0.8668504932016813</v>
       </c>
       <c r="Q37">
-        <v>0.8773637086704663</v>
+        <v>0.8773639268342946</v>
       </c>
     </row>
     <row r="38">
@@ -2431,49 +2431,49 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.01074060079991468</v>
+        <v>0.0107405552657831</v>
       </c>
       <c r="D38">
-        <v>0.07718364401649114</v>
+        <v>0.07718360840164318</v>
       </c>
       <c r="E38">
-        <v>0.1068824981174779</v>
+        <v>0.1068824974932171</v>
       </c>
       <c r="F38">
-        <v>0.2822985029153212</v>
+        <v>0.2822984899723837</v>
       </c>
       <c r="G38">
-        <v>0.4858617979015514</v>
+        <v>0.485861840180056</v>
       </c>
       <c r="H38">
-        <v>0.5114751405775092</v>
+        <v>0.5114751930142865</v>
       </c>
       <c r="I38">
-        <v>0.5494242864175134</v>
+        <v>0.5494243486365743</v>
       </c>
       <c r="J38">
-        <v>0.5993114344465345</v>
+        <v>0.5993115043467327</v>
       </c>
       <c r="K38">
-        <v>0.6301171977253086</v>
+        <v>0.6301172803161473</v>
       </c>
       <c r="L38">
-        <v>0.6603611822661543</v>
+        <v>0.6603612709696087</v>
       </c>
       <c r="M38">
-        <v>0.7054540008024308</v>
+        <v>0.7054541157803503</v>
       </c>
       <c r="N38">
-        <v>0.7352868311053065</v>
+        <v>0.7352869104117664</v>
       </c>
       <c r="O38">
-        <v>0.7796785438795588</v>
+        <v>0.7796786352571716</v>
       </c>
       <c r="P38">
-        <v>0.8194571520977161</v>
+        <v>0.8194572547319251</v>
       </c>
       <c r="Q38">
-        <v>0.842580323999166</v>
+        <v>0.8425804091263384</v>
       </c>
     </row>
     <row r="39">
@@ -2486,49 +2486,49 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0.01224839444641346</v>
+        <v>0.01224833924421109</v>
       </c>
       <c r="D39">
-        <v>0.07246795699831332</v>
+        <v>0.07246792370739641</v>
       </c>
       <c r="E39">
-        <v>0.1022205613853255</v>
+        <v>0.1022205594321081</v>
       </c>
       <c r="F39">
-        <v>0.2226389966208534</v>
+        <v>0.2226389781037993</v>
       </c>
       <c r="G39">
-        <v>0.3560089677224685</v>
+        <v>0.3560089781571905</v>
       </c>
       <c r="H39">
-        <v>0.3970952362821796</v>
+        <v>0.3970952565112642</v>
       </c>
       <c r="I39">
-        <v>0.5047884805489243</v>
+        <v>0.5047885146630726</v>
       </c>
       <c r="J39">
-        <v>0.5446745513671065</v>
+        <v>0.5446745954835925</v>
       </c>
       <c r="K39">
-        <v>0.6037132800326879</v>
+        <v>0.6037133578536693</v>
       </c>
       <c r="L39">
-        <v>0.6237435648768163</v>
+        <v>0.6237436461551931</v>
       </c>
       <c r="M39">
-        <v>0.6627677396535729</v>
+        <v>0.6627678132403493</v>
       </c>
       <c r="N39">
-        <v>0.6894414907362796</v>
+        <v>0.6894415817079127</v>
       </c>
       <c r="O39">
-        <v>0.7357169335549639</v>
+        <v>0.7357170315586186</v>
       </c>
       <c r="P39">
-        <v>0.7700789919466353</v>
+        <v>0.7700791036908404</v>
       </c>
       <c r="Q39">
-        <v>0.80595231228794</v>
+        <v>0.8059524136379883</v>
       </c>
     </row>
     <row r="40">
@@ -2541,49 +2541,49 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0.02630417099022586</v>
+        <v>0.02630414496742284</v>
       </c>
       <c r="D40">
-        <v>0.05260608035904146</v>
+        <v>0.05260607275844476</v>
       </c>
       <c r="E40">
-        <v>0.2020703846161707</v>
+        <v>0.2020703732494967</v>
       </c>
       <c r="F40">
-        <v>0.2417112121974203</v>
+        <v>0.2417112447106566</v>
       </c>
       <c r="G40">
-        <v>0.4628603192951344</v>
+        <v>0.4628603760183563</v>
       </c>
       <c r="H40">
-        <v>0.5329846983481894</v>
+        <v>0.532984762506544</v>
       </c>
       <c r="I40">
-        <v>0.6037970420328932</v>
+        <v>0.6037971480881749</v>
       </c>
       <c r="J40">
-        <v>0.661941911830464</v>
+        <v>0.6619420154572601</v>
       </c>
       <c r="K40">
-        <v>0.721043637659341</v>
+        <v>0.7210437327861294</v>
       </c>
       <c r="L40">
-        <v>0.7713308695174464</v>
+        <v>0.771330988708252</v>
       </c>
       <c r="M40">
-        <v>0.792721924329597</v>
+        <v>0.7927220454810863</v>
       </c>
       <c r="N40">
-        <v>0.8142059041303132</v>
+        <v>0.8142060341202723</v>
       </c>
       <c r="O40">
-        <v>0.8347644974542389</v>
+        <v>0.8347646029575324</v>
       </c>
       <c r="P40">
-        <v>0.8516960570938922</v>
+        <v>0.8516961682947548</v>
       </c>
       <c r="Q40">
-        <v>0.8710790957355344</v>
+        <v>0.871079176266025</v>
       </c>
     </row>
     <row r="41">
@@ -2596,49 +2596,49 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.05362802275242029</v>
+        <v>0.05362804001184829</v>
       </c>
       <c r="D41">
-        <v>0.2200556983661307</v>
+        <v>0.2200557026203183</v>
       </c>
       <c r="E41">
-        <v>0.309544042863932</v>
+        <v>0.3095440223636039</v>
       </c>
       <c r="F41">
-        <v>0.4001592124102216</v>
+        <v>0.4001592320573799</v>
       </c>
       <c r="G41">
-        <v>0.5110008638810387</v>
+        <v>0.5110008887135853</v>
       </c>
       <c r="H41">
-        <v>0.5610105339301721</v>
+        <v>0.5610105669155357</v>
       </c>
       <c r="I41">
-        <v>0.625688988665563</v>
+        <v>0.6256890160924587</v>
       </c>
       <c r="J41">
-        <v>0.6744849580469233</v>
+        <v>0.674485000142881</v>
       </c>
       <c r="K41">
-        <v>0.7081933019789034</v>
+        <v>0.708193344309753</v>
       </c>
       <c r="L41">
-        <v>0.7403355567445029</v>
+        <v>0.7403356064560846</v>
       </c>
       <c r="M41">
-        <v>0.7752745495214113</v>
+        <v>0.7752745998738364</v>
       </c>
       <c r="N41">
-        <v>0.8153325684551109</v>
+        <v>0.8153326121384463</v>
       </c>
       <c r="O41">
-        <v>0.8406017519974903</v>
+        <v>0.8406017880142338</v>
       </c>
       <c r="P41">
-        <v>0.8622471465222349</v>
+        <v>0.8622471773466033</v>
       </c>
       <c r="Q41">
-        <v>0.8823134450544117</v>
+        <v>0.8823134693561594</v>
       </c>
     </row>
     <row r="42">
@@ -2651,49 +2651,49 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.0384130121027757</v>
+        <v>0.03841300699879935</v>
       </c>
       <c r="D42">
-        <v>0.3070871381670568</v>
+        <v>0.3070872636826536</v>
       </c>
       <c r="E42">
-        <v>0.3699993999528993</v>
+        <v>0.3699996698884568</v>
       </c>
       <c r="F42">
-        <v>0.4815049079877681</v>
+        <v>0.4815050144471222</v>
       </c>
       <c r="G42">
-        <v>0.544224892100877</v>
+        <v>0.5442249220275416</v>
       </c>
       <c r="H42">
-        <v>0.6189282298273387</v>
+        <v>0.6189282124295213</v>
       </c>
       <c r="I42">
-        <v>0.6785561556613604</v>
+        <v>0.6785561940686824</v>
       </c>
       <c r="J42">
-        <v>0.7149168262333749</v>
+        <v>0.7149168353518999</v>
       </c>
       <c r="K42">
-        <v>0.7457651400167103</v>
+        <v>0.7457651861599052</v>
       </c>
       <c r="L42">
-        <v>0.7867740198230747</v>
+        <v>0.7867740671380836</v>
       </c>
       <c r="M42">
-        <v>0.814175904437616</v>
+        <v>0.8141759538882232</v>
       </c>
       <c r="N42">
-        <v>0.8575930151879002</v>
+        <v>0.8575930692434468</v>
       </c>
       <c r="O42">
-        <v>0.880664804844596</v>
+        <v>0.8806648613491047</v>
       </c>
       <c r="P42">
-        <v>0.8940453769198531</v>
+        <v>0.8940454209164049</v>
       </c>
       <c r="Q42">
-        <v>0.9181086367245603</v>
+        <v>0.9181086767028063</v>
       </c>
     </row>
     <row r="43">
@@ -2706,49 +2706,49 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0.03103074304490128</v>
+        <v>0.03103075566574554</v>
       </c>
       <c r="D43">
-        <v>0.1243888064224506</v>
+        <v>0.1243888078913347</v>
       </c>
       <c r="E43">
-        <v>0.3578139561512592</v>
+        <v>0.3578140527698472</v>
       </c>
       <c r="F43">
-        <v>0.4711619093876601</v>
+        <v>0.4711619022065789</v>
       </c>
       <c r="G43">
-        <v>0.5331274565750248</v>
+        <v>0.5331274671549588</v>
       </c>
       <c r="H43">
-        <v>0.5876706426852916</v>
+        <v>0.587670655607504</v>
       </c>
       <c r="I43">
-        <v>0.657470525901682</v>
+        <v>0.657470543084557</v>
       </c>
       <c r="J43">
-        <v>0.6955646135346253</v>
+        <v>0.695564641262001</v>
       </c>
       <c r="K43">
-        <v>0.7585301926271287</v>
+        <v>0.7585302084753984</v>
       </c>
       <c r="L43">
-        <v>0.7986975672684997</v>
+        <v>0.7986975950690004</v>
       </c>
       <c r="M43">
-        <v>0.8271970173643289</v>
+        <v>0.8271970491309224</v>
       </c>
       <c r="N43">
-        <v>0.855154350842119</v>
+        <v>0.8551543896365557</v>
       </c>
       <c r="O43">
-        <v>0.8760788149359742</v>
+        <v>0.8760788466529498</v>
       </c>
       <c r="P43">
-        <v>0.8907410957874282</v>
+        <v>0.890741127762619</v>
       </c>
       <c r="Q43">
-        <v>0.9046701122473169</v>
+        <v>0.9046701505114183</v>
       </c>
     </row>
   </sheetData>
